--- a/sheets/Libetee_楽天_8月作戦_2026.xlsx
+++ b/sheets/Libetee_楽天_8月作戦_2026.xlsx
@@ -20,12 +20,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="m/d(aaa)"/>
-    <numFmt numFmtId="166" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="167" formatCode="¥#,##0"/>
-    <numFmt numFmtId="168" formatCode="0.00&quot;%&quot;"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="m/d(aaa)"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="¥#,##0"/>
+    <numFmt numFmtId="167" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -118,7 +117,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -140,18 +139,62 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -160,13 +203,13 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -175,13 +218,13 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,13 +233,13 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -205,13 +248,13 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -220,28 +263,28 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -250,31 +293,31 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="167" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -313,6 +356,87 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -749,7 +873,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
+      <c r="A4" s="61" t="n">
         <v>46235</v>
       </c>
       <c r="B4" s="5" t="inlineStr">
@@ -763,10 +887,10 @@
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="62" t="n">
         <v>1.46</v>
       </c>
-      <c r="F4" s="8" t="n">
+      <c r="F4" s="63" t="n">
         <v>1080550</v>
       </c>
       <c r="G4" s="5" t="inlineStr">
@@ -781,7 +905,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="n">
+      <c r="A5" s="64" t="n">
         <v>46236</v>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -795,10 +919,10 @@
         </is>
       </c>
       <c r="D5" s="10" t="inlineStr"/>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F5" s="13" t="n">
+      <c r="F5" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -813,7 +937,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="n">
+      <c r="A6" s="64" t="n">
         <v>46237</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
@@ -827,10 +951,10 @@
         </is>
       </c>
       <c r="D6" s="10" t="inlineStr"/>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G6" s="10" t="inlineStr">
@@ -845,7 +969,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="14" t="n">
+      <c r="A7" s="67" t="n">
         <v>46238</v>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -859,10 +983,10 @@
         </is>
       </c>
       <c r="D7" s="15" t="inlineStr"/>
-      <c r="E7" s="17" t="n">
+      <c r="E7" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -877,7 +1001,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="70" t="n">
         <v>46239</v>
       </c>
       <c r="B8" s="20" t="inlineStr">
@@ -895,10 +1019,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="71" t="n">
         <v>3.02</v>
       </c>
-      <c r="F8" s="23" t="n">
+      <c r="F8" s="72" t="n">
         <v>2235111</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
@@ -913,7 +1037,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="67" t="n">
         <v>46240</v>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -927,10 +1051,10 @@
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr"/>
-      <c r="E9" s="17" t="n">
+      <c r="E9" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G9" s="15" t="inlineStr">
@@ -945,7 +1069,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="14" t="n">
+      <c r="A10" s="67" t="n">
         <v>46241</v>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -959,10 +1083,10 @@
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr"/>
-      <c r="E10" s="17" t="n">
+      <c r="E10" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F10" s="18" t="n">
+      <c r="F10" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G10" s="15" t="inlineStr">
@@ -977,7 +1101,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="14" t="n">
+      <c r="A11" s="67" t="n">
         <v>46242</v>
       </c>
       <c r="B11" s="15" t="inlineStr">
@@ -991,10 +1115,10 @@
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr"/>
-      <c r="E11" s="17" t="n">
+      <c r="E11" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F11" s="18" t="n">
+      <c r="F11" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G11" s="15" t="inlineStr">
@@ -1009,7 +1133,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="67" t="n">
         <v>46243</v>
       </c>
       <c r="B12" s="15" t="inlineStr">
@@ -1023,10 +1147,10 @@
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr"/>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F12" s="18" t="n">
+      <c r="F12" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G12" s="15" t="inlineStr">
@@ -1041,7 +1165,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
+      <c r="A13" s="70" t="n">
         <v>46244</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
@@ -1059,10 +1183,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E13" s="22" t="n">
+      <c r="E13" s="71" t="n">
         <v>3.02</v>
       </c>
-      <c r="F13" s="23" t="n">
+      <c r="F13" s="72" t="n">
         <v>2235111</v>
       </c>
       <c r="G13" s="20" t="inlineStr">
@@ -1077,7 +1201,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="14" t="n">
+      <c r="A14" s="67" t="n">
         <v>46245</v>
       </c>
       <c r="B14" s="15" t="inlineStr">
@@ -1091,10 +1215,10 @@
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr"/>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="F14" s="18" t="n">
+      <c r="F14" s="69" t="n">
         <v>821514</v>
       </c>
       <c r="G14" s="15" t="inlineStr">
@@ -1109,7 +1233,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="n">
+      <c r="A15" s="64" t="n">
         <v>46246</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
@@ -1123,10 +1247,10 @@
         </is>
       </c>
       <c r="D15" s="10" t="inlineStr"/>
-      <c r="E15" s="12" t="n">
+      <c r="E15" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G15" s="10" t="inlineStr">
@@ -1141,7 +1265,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="n">
+      <c r="A16" s="64" t="n">
         <v>46247</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
@@ -1155,10 +1279,10 @@
         </is>
       </c>
       <c r="D16" s="10" t="inlineStr"/>
-      <c r="E16" s="12" t="n">
+      <c r="E16" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G16" s="10" t="inlineStr">
@@ -1173,7 +1297,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="n">
+      <c r="A17" s="64" t="n">
         <v>46248</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
@@ -1187,10 +1311,10 @@
         </is>
       </c>
       <c r="D17" s="10" t="inlineStr"/>
-      <c r="E17" s="12" t="n">
+      <c r="E17" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="13" t="n">
+      <c r="F17" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G17" s="10" t="inlineStr">
@@ -1205,7 +1329,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="73" t="n">
         <v>46249</v>
       </c>
       <c r="B18" s="25" t="inlineStr">
@@ -1223,10 +1347,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="74" t="n">
         <v>2.2</v>
       </c>
-      <c r="F18" s="28" t="n">
+      <c r="F18" s="75" t="n">
         <v>1628227</v>
       </c>
       <c r="G18" s="25" t="inlineStr">
@@ -1241,7 +1365,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="n">
+      <c r="A19" s="64" t="n">
         <v>46250</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
@@ -1255,10 +1379,10 @@
         </is>
       </c>
       <c r="D19" s="10" t="inlineStr"/>
-      <c r="E19" s="12" t="n">
+      <c r="E19" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G19" s="10" t="inlineStr">
@@ -1273,7 +1397,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="n">
+      <c r="A20" s="64" t="n">
         <v>46251</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
@@ -1287,10 +1411,10 @@
         </is>
       </c>
       <c r="D20" s="10" t="inlineStr"/>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="13" t="n">
+      <c r="F20" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G20" s="10" t="inlineStr">
@@ -1305,7 +1429,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="n">
+      <c r="A21" s="64" t="n">
         <v>46252</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
@@ -1319,10 +1443,10 @@
         </is>
       </c>
       <c r="D21" s="10" t="inlineStr"/>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="13" t="n">
+      <c r="F21" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G21" s="10" t="inlineStr">
@@ -1337,7 +1461,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="n">
+      <c r="A22" s="64" t="n">
         <v>46253</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
@@ -1351,10 +1475,10 @@
         </is>
       </c>
       <c r="D22" s="10" t="inlineStr"/>
-      <c r="E22" s="12" t="n">
+      <c r="E22" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="13" t="n">
+      <c r="F22" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G22" s="10" t="inlineStr">
@@ -1369,7 +1493,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="n">
+      <c r="A23" s="73" t="n">
         <v>46254</v>
       </c>
       <c r="B23" s="25" t="inlineStr">
@@ -1387,10 +1511,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="74" t="n">
         <v>2.2</v>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F23" s="75" t="n">
         <v>1628227</v>
       </c>
       <c r="G23" s="25" t="inlineStr">
@@ -1405,7 +1529,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="n">
+      <c r="A24" s="64" t="n">
         <v>46255</v>
       </c>
       <c r="B24" s="10" t="inlineStr">
@@ -1419,10 +1543,10 @@
         </is>
       </c>
       <c r="D24" s="10" t="inlineStr"/>
-      <c r="E24" s="12" t="n">
+      <c r="E24" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F24" s="13" t="n">
+      <c r="F24" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G24" s="10" t="inlineStr">
@@ -1437,7 +1561,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="n">
+      <c r="A25" s="64" t="n">
         <v>46256</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
@@ -1451,10 +1575,10 @@
         </is>
       </c>
       <c r="D25" s="10" t="inlineStr"/>
-      <c r="E25" s="12" t="n">
+      <c r="E25" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F25" s="13" t="n">
+      <c r="F25" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G25" s="10" t="inlineStr">
@@ -1469,7 +1593,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="n">
+      <c r="A26" s="64" t="n">
         <v>46257</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
@@ -1483,10 +1607,10 @@
         </is>
       </c>
       <c r="D26" s="10" t="inlineStr"/>
-      <c r="E26" s="12" t="n">
+      <c r="E26" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="13" t="n">
+      <c r="F26" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G26" s="10" t="inlineStr">
@@ -1501,7 +1625,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="n">
+      <c r="A27" s="64" t="n">
         <v>46258</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
@@ -1515,10 +1639,10 @@
         </is>
       </c>
       <c r="D27" s="10" t="inlineStr"/>
-      <c r="E27" s="12" t="n">
+      <c r="E27" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="13" t="n">
+      <c r="F27" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G27" s="10" t="inlineStr">
@@ -1533,7 +1657,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="n">
+      <c r="A28" s="73" t="n">
         <v>46259</v>
       </c>
       <c r="B28" s="25" t="inlineStr">
@@ -1551,10 +1675,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E28" s="27" t="n">
+      <c r="E28" s="74" t="n">
         <v>2.2</v>
       </c>
-      <c r="F28" s="28" t="n">
+      <c r="F28" s="75" t="n">
         <v>1628227</v>
       </c>
       <c r="G28" s="25" t="inlineStr">
@@ -1569,7 +1693,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="n">
+      <c r="A29" s="64" t="n">
         <v>46260</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
@@ -1583,10 +1707,10 @@
         </is>
       </c>
       <c r="D29" s="10" t="inlineStr"/>
-      <c r="E29" s="12" t="n">
+      <c r="E29" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="13" t="n">
+      <c r="F29" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G29" s="10" t="inlineStr">
@@ -1601,7 +1725,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="n">
+      <c r="A30" s="64" t="n">
         <v>46261</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
@@ -1615,10 +1739,10 @@
         </is>
       </c>
       <c r="D30" s="10" t="inlineStr"/>
-      <c r="E30" s="12" t="n">
+      <c r="E30" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="13" t="n">
+      <c r="F30" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G30" s="10" t="inlineStr">
@@ -1633,7 +1757,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="n">
+      <c r="A31" s="64" t="n">
         <v>46262</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
@@ -1647,10 +1771,10 @@
         </is>
       </c>
       <c r="D31" s="10" t="inlineStr"/>
-      <c r="E31" s="12" t="n">
+      <c r="E31" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="13" t="n">
+      <c r="F31" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G31" s="10" t="inlineStr">
@@ -1665,7 +1789,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="9" t="n">
+      <c r="A32" s="64" t="n">
         <v>46263</v>
       </c>
       <c r="B32" s="10" t="inlineStr">
@@ -1679,10 +1803,10 @@
         </is>
       </c>
       <c r="D32" s="10" t="inlineStr"/>
-      <c r="E32" s="12" t="n">
+      <c r="E32" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F32" s="13" t="n">
+      <c r="F32" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G32" s="10" t="inlineStr">
@@ -1697,7 +1821,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="24" t="n">
+      <c r="A33" s="73" t="n">
         <v>46264</v>
       </c>
       <c r="B33" s="25" t="inlineStr">
@@ -1715,10 +1839,10 @@
           <t>●</t>
         </is>
       </c>
-      <c r="E33" s="27" t="n">
+      <c r="E33" s="74" t="n">
         <v>2.2</v>
       </c>
-      <c r="F33" s="28" t="n">
+      <c r="F33" s="75" t="n">
         <v>1628227</v>
       </c>
       <c r="G33" s="25" t="inlineStr">
@@ -1733,7 +1857,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="9" t="n">
+      <c r="A34" s="64" t="n">
         <v>46265</v>
       </c>
       <c r="B34" s="10" t="inlineStr">
@@ -1747,10 +1871,10 @@
         </is>
       </c>
       <c r="D34" s="10" t="inlineStr"/>
-      <c r="E34" s="12" t="n">
+      <c r="E34" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="13" t="n">
+      <c r="F34" s="66" t="n">
         <v>740103</v>
       </c>
       <c r="G34" s="10" t="inlineStr">
@@ -1770,11 +1894,11 @@
           <t>月商予測</t>
         </is>
       </c>
-      <c r="B35" s="30" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="31" t="n">
+      <c r="B35" s="76" t="n"/>
+      <c r="C35" s="76" t="n"/>
+      <c r="D35" s="76" t="n"/>
+      <c r="E35" s="77" t="n"/>
+      <c r="F35" s="78" t="n">
         <v>30314618</v>
       </c>
       <c r="G35" s="29" t="inlineStr">
@@ -1863,16 +1987,16 @@
       <c r="B3" s="33" t="n">
         <v>4</v>
       </c>
-      <c r="C3" s="34" t="n">
+      <c r="C3" s="79" t="n">
         <v>3567832</v>
       </c>
-      <c r="D3" s="35" t="n">
+      <c r="D3" s="80" t="n">
         <v>4.82</v>
       </c>
-      <c r="E3" s="36" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="F3" s="34" t="n">
+      <c r="E3" s="81" t="n">
+        <v>0.0066</v>
+      </c>
+      <c r="F3" s="79" t="n">
         <v>30429</v>
       </c>
     </row>
@@ -1885,16 +2009,16 @@
       <c r="B4" s="38" t="n">
         <v>10</v>
       </c>
-      <c r="C4" s="39" t="n">
+      <c r="C4" s="82" t="n">
         <v>2234584</v>
       </c>
-      <c r="D4" s="40" t="n">
+      <c r="D4" s="83" t="n">
         <v>3.02</v>
       </c>
-      <c r="E4" s="41" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="F4" s="39" t="n">
+      <c r="E4" s="84" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="F4" s="82" t="n">
         <v>24801</v>
       </c>
     </row>
@@ -1907,16 +2031,16 @@
       <c r="B5" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="75" t="n">
         <v>1631874</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="74" t="n">
         <v>2.2</v>
       </c>
-      <c r="E5" s="42" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F5" s="28" t="n">
+      <c r="E5" s="85" t="n">
+        <v>0.0046</v>
+      </c>
+      <c r="F5" s="75" t="n">
         <v>20127</v>
       </c>
     </row>
@@ -1929,16 +2053,16 @@
       <c r="B6" s="15" t="n">
         <v>12</v>
       </c>
-      <c r="C6" s="18" t="n">
+      <c r="C6" s="69" t="n">
         <v>1158456</v>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="68" t="n">
         <v>1.57</v>
       </c>
-      <c r="E6" s="43" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F6" s="18" t="n">
+      <c r="E6" s="86" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F6" s="69" t="n">
         <v>30286</v>
       </c>
     </row>
@@ -1951,16 +2075,16 @@
       <c r="B7" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="C7" s="8" t="n">
+      <c r="C7" s="63" t="n">
         <v>1081629</v>
       </c>
-      <c r="D7" s="7" t="n">
+      <c r="D7" s="62" t="n">
         <v>1.46</v>
       </c>
-      <c r="E7" s="44" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F7" s="8" t="n">
+      <c r="E7" s="87" t="n">
+        <v>0.0035</v>
+      </c>
+      <c r="F7" s="63" t="n">
         <v>30653</v>
       </c>
     </row>
@@ -1973,16 +2097,16 @@
       <c r="B8" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="C8" s="18" t="n">
+      <c r="C8" s="69" t="n">
         <v>824846</v>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="68" t="n">
         <v>1.11</v>
       </c>
-      <c r="E8" s="43" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F8" s="18" t="n">
+      <c r="E8" s="86" t="n">
+        <v>0.0026</v>
+      </c>
+      <c r="F8" s="69" t="n">
         <v>24236</v>
       </c>
     </row>
@@ -1995,19 +2119,20 @@
       <c r="B9" s="10" t="n">
         <v>118</v>
       </c>
-      <c r="C9" s="13" t="n">
+      <c r="C9" s="66" t="n">
         <v>740103</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="65" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="45" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="F9" s="13" t="n">
+      <c r="E9" s="88" t="n">
+        <v>0.0022</v>
+      </c>
+      <c r="F9" s="66" t="n">
         <v>22838</v>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
@@ -2087,13 +2212,13 @@
           <t>2026-01</t>
         </is>
       </c>
-      <c r="B3" s="47" t="n">
+      <c r="B3" s="89" t="n">
         <v>21775522</v>
       </c>
       <c r="C3" s="46" t="n">
         <v>31</v>
       </c>
-      <c r="D3" s="47" t="n">
+      <c r="D3" s="89" t="n">
         <v>702436</v>
       </c>
     </row>
@@ -2103,13 +2228,13 @@
           <t>2026-02</t>
         </is>
       </c>
-      <c r="B4" s="47" t="n">
+      <c r="B4" s="89" t="n">
         <v>21626250</v>
       </c>
       <c r="C4" s="46" t="n">
         <v>28</v>
       </c>
-      <c r="D4" s="47" t="n">
+      <c r="D4" s="89" t="n">
         <v>772366</v>
       </c>
     </row>
@@ -2119,13 +2244,13 @@
           <t>2026-03</t>
         </is>
       </c>
-      <c r="B5" s="47" t="n">
+      <c r="B5" s="89" t="n">
         <v>30688230</v>
       </c>
       <c r="C5" s="46" t="n">
         <v>31</v>
       </c>
-      <c r="D5" s="47" t="n">
+      <c r="D5" s="89" t="n">
         <v>989943</v>
       </c>
     </row>
@@ -2135,13 +2260,13 @@
           <t>2026-04</t>
         </is>
       </c>
-      <c r="B6" s="47" t="n">
+      <c r="B6" s="89" t="n">
         <v>35044550</v>
       </c>
       <c r="C6" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="D6" s="47" t="n">
+      <c r="D6" s="89" t="n">
         <v>1168152</v>
       </c>
     </row>
@@ -2151,13 +2276,13 @@
           <t>2026-05</t>
         </is>
       </c>
-      <c r="B7" s="47" t="n">
+      <c r="B7" s="89" t="n">
         <v>26108970</v>
       </c>
       <c r="C7" s="46" t="n">
         <v>31</v>
       </c>
-      <c r="D7" s="47" t="n">
+      <c r="D7" s="89" t="n">
         <v>842225</v>
       </c>
     </row>
@@ -2167,13 +2292,13 @@
           <t>2026-06</t>
         </is>
       </c>
-      <c r="B8" s="47" t="n">
+      <c r="B8" s="89" t="n">
         <v>33432028</v>
       </c>
       <c r="C8" s="46" t="n">
         <v>30</v>
       </c>
-      <c r="D8" s="47" t="n">
+      <c r="D8" s="89" t="n">
         <v>1114401</v>
       </c>
     </row>
@@ -2183,13 +2308,13 @@
           <t>2026-07</t>
         </is>
       </c>
-      <c r="B9" s="47" t="n">
+      <c r="B9" s="89" t="n">
         <v>43920694</v>
       </c>
       <c r="C9" s="46" t="n">
         <v>26</v>
       </c>
-      <c r="D9" s="47" t="n">
+      <c r="D9" s="89" t="n">
         <v>1689257</v>
       </c>
     </row>
@@ -2199,12 +2324,13 @@
           <t>合計</t>
         </is>
       </c>
-      <c r="B10" s="31" t="n">
+      <c r="B10" s="78" t="n">
         <v>212596244</v>
       </c>
       <c r="C10" s="29" t="n"/>
       <c r="D10" s="29" t="n"/>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>

--- a/sheets/Libetee_楽天_8月作戦_2026.xlsx
+++ b/sheets/Libetee_楽天_8月作戦_2026.xlsx
@@ -873,8 +873,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="61" t="n">
-        <v>46235</v>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>8/1(土)</t>
+        </is>
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
@@ -905,8 +907,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="64" t="n">
-        <v>46236</v>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>8/2(日)</t>
+        </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
         <is>
@@ -937,8 +941,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="64" t="n">
-        <v>46237</v>
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t>8/3(月)</t>
+        </is>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -969,8 +975,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="67" t="n">
-        <v>46238</v>
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>8/4(火)</t>
+        </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
@@ -1001,8 +1009,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="70" t="n">
-        <v>46239</v>
+      <c r="A8" s="20" t="inlineStr">
+        <is>
+          <t>8/5(水)</t>
+        </is>
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
@@ -1037,8 +1047,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="67" t="n">
-        <v>46240</v>
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>8/6(木)</t>
+        </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
@@ -1069,8 +1081,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="67" t="n">
-        <v>46241</v>
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>8/7(金)</t>
+        </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
         <is>
@@ -1101,8 +1115,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="67" t="n">
-        <v>46242</v>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>8/8(土)</t>
+        </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
@@ -1133,8 +1149,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="67" t="n">
-        <v>46243</v>
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>8/9(日)</t>
+        </is>
       </c>
       <c r="B12" s="15" t="inlineStr">
         <is>
@@ -1165,8 +1183,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="70" t="n">
-        <v>46244</v>
+      <c r="A13" s="20" t="inlineStr">
+        <is>
+          <t>8/10(月)</t>
+        </is>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
@@ -1201,8 +1221,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="67" t="n">
-        <v>46245</v>
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>8/11(火)</t>
+        </is>
       </c>
       <c r="B14" s="15" t="inlineStr">
         <is>
@@ -1233,8 +1255,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="64" t="n">
-        <v>46246</v>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t>8/12(水)</t>
+        </is>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -1265,8 +1289,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="64" t="n">
-        <v>46247</v>
+      <c r="A16" s="10" t="inlineStr">
+        <is>
+          <t>8/13(木)</t>
+        </is>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1297,8 +1323,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="64" t="n">
-        <v>46248</v>
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t>8/14(金)</t>
+        </is>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1329,8 +1357,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="73" t="n">
-        <v>46249</v>
+      <c r="A18" s="25" t="inlineStr">
+        <is>
+          <t>8/15(土)</t>
+        </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
@@ -1365,8 +1395,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="64" t="n">
-        <v>46250</v>
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t>8/16(日)</t>
+        </is>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1397,8 +1429,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="64" t="n">
-        <v>46251</v>
+      <c r="A20" s="10" t="inlineStr">
+        <is>
+          <t>8/17(月)</t>
+        </is>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1429,8 +1463,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="64" t="n">
-        <v>46252</v>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t>8/18(火)</t>
+        </is>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1461,8 +1497,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="64" t="n">
-        <v>46253</v>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t>8/19(水)</t>
+        </is>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1493,8 +1531,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="73" t="n">
-        <v>46254</v>
+      <c r="A23" s="25" t="inlineStr">
+        <is>
+          <t>8/20(木)</t>
+        </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
@@ -1529,8 +1569,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="64" t="n">
-        <v>46255</v>
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>8/21(金)</t>
+        </is>
       </c>
       <c r="B24" s="10" t="inlineStr">
         <is>
@@ -1561,8 +1603,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="64" t="n">
-        <v>46256</v>
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>8/22(土)</t>
+        </is>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1593,8 +1637,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="64" t="n">
-        <v>46257</v>
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>8/23(日)</t>
+        </is>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1625,8 +1671,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="64" t="n">
-        <v>46258</v>
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>8/24(月)</t>
+        </is>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1657,8 +1705,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="73" t="n">
-        <v>46259</v>
+      <c r="A28" s="25" t="inlineStr">
+        <is>
+          <t>8/25(火)</t>
+        </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
@@ -1693,8 +1743,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="64" t="n">
-        <v>46260</v>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>8/26(水)</t>
+        </is>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1725,8 +1777,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="64" t="n">
-        <v>46261</v>
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>8/27(木)</t>
+        </is>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1757,8 +1811,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="64" t="n">
-        <v>46262</v>
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>8/28(金)</t>
+        </is>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1789,8 +1845,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="64" t="n">
-        <v>46263</v>
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>8/29(土)</t>
+        </is>
       </c>
       <c r="B32" s="10" t="inlineStr">
         <is>
@@ -1821,8 +1879,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="73" t="n">
-        <v>46264</v>
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>8/30(日)</t>
+        </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
@@ -1857,8 +1917,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="64" t="n">
-        <v>46265</v>
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>8/31(月)</t>
+        </is>
       </c>
       <c r="B34" s="10" t="inlineStr">
         <is>
